--- a/数值知识库-网页版GPT/源表/B-ObjectLibrary-编辑器物件表.xlsx
+++ b/数值知识库-网页版GPT/源表/B-ObjectLibrary-编辑器物件表.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1610">
   <si>
     <t>##var</t>
   </si>
@@ -5866,6 +5866,9 @@
   <si>
     <t>失败后会回到最后激活的位置，仅对战斗区域有效</t>
     <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>3:4</t>
   </si>
 </sst>
 </file>
@@ -20034,7 +20037,7 @@
         <v>408</v>
       </c>
       <c r="L298" s="2" t="s">
-        <v>331</v>
+        <v>1609</v>
       </c>
       <c r="M298" t="s">
         <v>1564</v>
